--- a/artfynd/A 61313-2019 artfynd.xlsx
+++ b/artfynd/A 61313-2019 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 61313-2019 artfynd.xlsx
+++ b/artfynd/A 61313-2019 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>121115249</v>
       </c>
       <c r="B3" t="n">
-        <v>57459</v>
+        <v>57462</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 61313-2019 artfynd.xlsx
+++ b/artfynd/A 61313-2019 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>121115249</v>
       </c>
       <c r="B3" t="n">
-        <v>57462</v>
+        <v>57465</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 61313-2019 artfynd.xlsx
+++ b/artfynd/A 61313-2019 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -907,6 +907,240 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>125730759</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57257</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>102964</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Fiskmås</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Larus canus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Aitejokk, Holmajärvi, T lm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>700028</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7530875</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>08:02</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>08:02</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Ros-Marie Andersson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Ros-Marie Andersson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>125818525</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58083</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>102999</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Björktrast</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Turdus pilaris</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>bo, ägg/ungar</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Aitejokk, Holmajärvi, T lm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>700028</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7530875</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>02:41</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>02:41</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Ros-Marie Andersson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Ros-Marie Andersson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 61313-2019 artfynd.xlsx
+++ b/artfynd/A 61313-2019 artfynd.xlsx
@@ -1032,7 +1032,7 @@
         <v>125818525</v>
       </c>
       <c r="B5" t="n">
-        <v>58083</v>
+        <v>58084</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 61313-2019 artfynd.xlsx
+++ b/artfynd/A 61313-2019 artfynd.xlsx
@@ -913,7 +913,7 @@
         <v>125730759</v>
       </c>
       <c r="B4" t="n">
-        <v>57257</v>
+        <v>57258</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1032,7 +1032,7 @@
         <v>125818525</v>
       </c>
       <c r="B5" t="n">
-        <v>58084</v>
+        <v>58085</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 61313-2019 artfynd.xlsx
+++ b/artfynd/A 61313-2019 artfynd.xlsx
@@ -913,7 +913,7 @@
         <v>125730759</v>
       </c>
       <c r="B4" t="n">
-        <v>57258</v>
+        <v>57262</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1032,7 +1032,7 @@
         <v>125818525</v>
       </c>
       <c r="B5" t="n">
-        <v>58085</v>
+        <v>58089</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 61313-2019 artfynd.xlsx
+++ b/artfynd/A 61313-2019 artfynd.xlsx
@@ -913,7 +913,7 @@
         <v>125730759</v>
       </c>
       <c r="B4" t="n">
-        <v>57262</v>
+        <v>57263</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1032,7 +1032,7 @@
         <v>125818525</v>
       </c>
       <c r="B5" t="n">
-        <v>58089</v>
+        <v>58092</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
